--- a/tests/global_summary.xlsx
+++ b/tests/global_summary.xlsx
@@ -1321,17 +1321,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1370,10 +1366,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1412,10 +1406,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1454,10 +1446,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1496,10 +1486,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A7" t="n">
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1538,10 +1526,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A8" t="n">
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1580,10 +1566,8 @@
       </c>
     </row>
     <row r="9" hidden="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A9" t="n">
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1622,10 +1606,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A10" t="n">
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1664,10 +1646,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A11" t="n">
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1706,10 +1686,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A12" t="n">
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1748,10 +1726,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A13" t="n">
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1790,10 +1766,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A14" t="n">
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1832,10 +1806,8 @@
       </c>
     </row>
     <row r="15" hidden="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A15" t="n">
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1874,10 +1846,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A16" t="n">
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1916,10 +1886,8 @@
       </c>
     </row>
     <row r="17" customFormat="1" s="1">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A17" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
@@ -1958,10 +1926,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A18" t="n">
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2000,10 +1966,8 @@
       </c>
     </row>
     <row r="19" hidden="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A19" t="n">
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2042,10 +2006,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A20" t="n">
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2084,10 +2046,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="A21" t="n">
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
